--- a/simulations/hydro/inputs/Scenarios_26-08-04.xlsx
+++ b/simulations/hydro/inputs/Scenarios_26-08-04.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1946" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1951" uniqueCount="580">
   <si>
     <t xml:space="preserve">Input</t>
   </si>
@@ -1619,16 +1619,13 @@
     <t xml:space="preserve">Vmax parameter for amino acids xylem loading</t>
   </si>
   <si>
-    <t xml:space="preserve">SIGMA_SUCROSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cnwheat</t>
+    <t xml:space="preserve">hydraulics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shoot</t>
   </si>
   <si>
     <t xml:space="preserve">Conductance parameter </t>
-  </si>
-  <si>
-    <t xml:space="preserve">g2.mol-1.m-2.s-1</t>
   </si>
   <si>
     <t xml:space="preserve">water_moisture_patch</t>
@@ -2517,7 +2514,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AW239"/>
+  <dimension ref="A1:AW1048576"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.71"/>
@@ -10767,40 +10764,36 @@
         <v>32</v>
       </c>
       <c r="C227" s="8" t="s">
+        <v>532</v>
+      </c>
+      <c r="D227" s="8" t="s">
         <v>533</v>
-      </c>
-      <c r="D227" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="E227" s="59" t="s">
         <v>534</v>
       </c>
       <c r="F227" s="59" t="s">
-        <v>535</v>
-      </c>
-      <c r="G227" s="10" t="n">
-        <v>1E-007</v>
-      </c>
-      <c r="I227" s="10" t="n">
-        <f aca="false">0.0000001</f>
-        <v>1E-007</v>
-      </c>
-      <c r="J227" s="10" t="n">
-        <f aca="false">0.0000001</f>
-        <v>1E-007</v>
-      </c>
-      <c r="K227" s="10" t="n">
-        <f aca="false">0.0000001</f>
-        <v>1E-007</v>
-      </c>
-      <c r="L227" s="10" t="n">
-        <f aca="false">0.0000001</f>
-        <v>1E-007</v>
+        <v>34</v>
+      </c>
+      <c r="G227" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I227" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="J227" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="K227" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="L227" s="10" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B228" s="8" t="s">
         <v>32</v>
@@ -10812,7 +10805,7 @@
         <v>14</v>
       </c>
       <c r="E228" s="59" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F228" s="59" t="s">
         <v>496</v>
@@ -10858,7 +10851,7 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B229" s="8" t="s">
         <v>32</v>
@@ -10870,7 +10863,7 @@
         <v>488</v>
       </c>
       <c r="E229" s="59" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F229" s="59" t="s">
         <v>499</v>
@@ -10916,7 +10909,7 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B230" s="8" t="s">
         <v>32</v>
@@ -10928,7 +10921,7 @@
         <v>488</v>
       </c>
       <c r="E230" s="59" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F230" s="59" t="s">
         <v>499</v>
@@ -10979,7 +10972,7 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B231" s="8" t="s">
         <v>32</v>
@@ -10991,7 +10984,7 @@
         <v>488</v>
       </c>
       <c r="E231" s="59" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F231" s="59" t="s">
         <v>499</v>
@@ -11037,7 +11030,7 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B232" s="8" t="s">
         <v>32</v>
@@ -11049,10 +11042,10 @@
         <v>14</v>
       </c>
       <c r="E232" s="59" t="s">
+        <v>544</v>
+      </c>
+      <c r="F232" s="59" t="s">
         <v>545</v>
-      </c>
-      <c r="F232" s="59" t="s">
-        <v>546</v>
       </c>
       <c r="G232" s="10" t="n">
         <v>1E-005</v>
@@ -11099,7 +11092,7 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B233" s="8" t="s">
         <v>32</v>
@@ -11111,7 +11104,7 @@
         <v>14</v>
       </c>
       <c r="E233" s="59" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F233" s="59" t="s">
         <v>499</v>
@@ -11161,7 +11154,7 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B234" s="8" t="s">
         <v>32</v>
@@ -11205,7 +11198,7 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B235" s="8" t="s">
         <v>32</v>
@@ -11249,7 +11242,7 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B236" s="8" t="s">
         <v>32</v>
@@ -11261,7 +11254,7 @@
         <v>14</v>
       </c>
       <c r="E236" s="54" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F236" s="54" t="s">
         <v>264</v>
@@ -11292,7 +11285,7 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="42" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B237" s="8" t="s">
         <v>32</v>
@@ -11304,10 +11297,10 @@
         <v>14</v>
       </c>
       <c r="E237" s="43" t="s">
+        <v>553</v>
+      </c>
+      <c r="F237" s="43" t="s">
         <v>554</v>
-      </c>
-      <c r="F237" s="43" t="s">
-        <v>555</v>
       </c>
       <c r="G237" s="10" t="n">
         <v>1E-009</v>
@@ -11331,7 +11324,7 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="42" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B238" s="8" t="s">
         <v>32</v>
@@ -11343,10 +11336,10 @@
         <v>14</v>
       </c>
       <c r="E238" s="43" t="s">
+        <v>553</v>
+      </c>
+      <c r="F238" s="43" t="s">
         <v>554</v>
-      </c>
-      <c r="F238" s="43" t="s">
-        <v>555</v>
       </c>
       <c r="G238" s="10" t="n">
         <v>1E-009</v>
@@ -11370,7 +11363,7 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B239" s="8" t="s">
         <v>32</v>
@@ -11382,10 +11375,10 @@
         <v>14</v>
       </c>
       <c r="E239" s="59" t="s">
+        <v>557</v>
+      </c>
+      <c r="F239" s="59" t="s">
         <v>558</v>
-      </c>
-      <c r="F239" s="59" t="s">
-        <v>559</v>
       </c>
       <c r="G239" s="59" t="n">
         <v>0.1</v>
@@ -11403,6 +11396,7 @@
         <v>0.01</v>
       </c>
     </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <conditionalFormatting sqref="I239:L239">
     <cfRule type="colorScale" priority="2">
@@ -11624,7 +11618,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G227">
+  <conditionalFormatting sqref="I2:L2">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -11646,7 +11640,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:L2">
+  <conditionalFormatting sqref="I3:L3 I5:L5">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -11668,7 +11662,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:L3 I5:L5">
+  <conditionalFormatting sqref="I6:L6 G227 I227:L227">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -11690,7 +11684,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I6:L6">
+  <conditionalFormatting sqref="I7:L7">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -11712,7 +11706,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:L7">
+  <conditionalFormatting sqref="I8:L8">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -11734,7 +11728,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I8:L8">
+  <conditionalFormatting sqref="I9:L9">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -11756,7 +11750,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9:L9">
+  <conditionalFormatting sqref="I10:L10">
     <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -11778,7 +11772,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I10:L10">
+  <conditionalFormatting sqref="I11:L11">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -11800,7 +11794,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11:L11">
+  <conditionalFormatting sqref="I12:L12">
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -11822,7 +11816,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I12:L12">
+  <conditionalFormatting sqref="I13:L13">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -11844,7 +11838,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I13:L13">
+  <conditionalFormatting sqref="I14:L14">
     <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -11866,7 +11860,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14:L14">
+  <conditionalFormatting sqref="I15:L15">
     <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -11888,7 +11882,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I15:L15">
+  <conditionalFormatting sqref="I16:L16">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -11910,7 +11904,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I16:L16">
+  <conditionalFormatting sqref="I17:L17">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -11932,7 +11926,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I17:L17">
+  <conditionalFormatting sqref="I18:L18">
     <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -11954,7 +11948,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I18:L18">
+  <conditionalFormatting sqref="I19:L19">
     <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -11976,7 +11970,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I19:L19">
+  <conditionalFormatting sqref="I20:L20">
     <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -11998,7 +11992,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I20:L20">
+  <conditionalFormatting sqref="I21:L21">
     <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12020,7 +12014,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I21:L21">
+  <conditionalFormatting sqref="I22:L22">
     <cfRule type="colorScale" priority="58">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12042,7 +12036,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I22:L22">
+  <conditionalFormatting sqref="I23:L23">
     <cfRule type="colorScale" priority="60">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12064,7 +12058,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I23:L23">
+  <conditionalFormatting sqref="I24:L25">
     <cfRule type="colorScale" priority="62">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12086,7 +12080,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I24:L25">
+  <conditionalFormatting sqref="I26:L26">
     <cfRule type="colorScale" priority="64">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12108,7 +12102,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I26:L26">
+  <conditionalFormatting sqref="I27:L27">
     <cfRule type="colorScale" priority="66">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12130,7 +12124,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I27:L27">
+  <conditionalFormatting sqref="I28:L28">
     <cfRule type="colorScale" priority="68">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12152,7 +12146,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I28:L28">
+  <conditionalFormatting sqref="I29:L29">
     <cfRule type="colorScale" priority="70">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12174,7 +12168,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I29:L29">
+  <conditionalFormatting sqref="I30:L30">
     <cfRule type="colorScale" priority="72">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12196,7 +12190,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I30:L30">
+  <conditionalFormatting sqref="I31:L31">
     <cfRule type="colorScale" priority="74">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12218,7 +12212,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I31:L31">
+  <conditionalFormatting sqref="I32:L32">
     <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12240,7 +12234,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I32:L32">
+  <conditionalFormatting sqref="I33:L33">
     <cfRule type="colorScale" priority="78">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12262,7 +12256,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I33:L33">
+  <conditionalFormatting sqref="I34:L34">
     <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12284,7 +12278,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I34:L34">
+  <conditionalFormatting sqref="I35:L35">
     <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12306,7 +12300,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I35:L35">
+  <conditionalFormatting sqref="I36:L36">
     <cfRule type="colorScale" priority="84">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12328,7 +12322,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I36:L36">
+  <conditionalFormatting sqref="I37:L37">
     <cfRule type="colorScale" priority="86">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12350,7 +12344,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I37:L37">
+  <conditionalFormatting sqref="I38:L38">
     <cfRule type="colorScale" priority="88">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12372,7 +12366,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I38:L38">
+  <conditionalFormatting sqref="I39:L39">
     <cfRule type="colorScale" priority="90">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12394,7 +12388,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I39:L39">
+  <conditionalFormatting sqref="I40:L40">
     <cfRule type="colorScale" priority="92">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12416,7 +12410,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I40:L40">
+  <conditionalFormatting sqref="I41:L41">
     <cfRule type="colorScale" priority="94">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12438,7 +12432,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I41:L41">
+  <conditionalFormatting sqref="I42:L42">
     <cfRule type="colorScale" priority="96">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12460,7 +12454,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I42:L42">
+  <conditionalFormatting sqref="I43:L43">
     <cfRule type="colorScale" priority="98">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12482,7 +12476,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I43:L43">
+  <conditionalFormatting sqref="I44:L44">
     <cfRule type="colorScale" priority="100">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12504,7 +12498,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I44:L44">
+  <conditionalFormatting sqref="I45:L45">
     <cfRule type="colorScale" priority="102">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12526,7 +12520,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I45:L45">
+  <conditionalFormatting sqref="I46:L46">
     <cfRule type="colorScale" priority="104">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12548,7 +12542,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I46:L46">
+  <conditionalFormatting sqref="I47:L47">
     <cfRule type="colorScale" priority="106">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12570,7 +12564,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I47:L47">
+  <conditionalFormatting sqref="I48:L48">
     <cfRule type="colorScale" priority="108">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12592,7 +12586,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I48:L48">
+  <conditionalFormatting sqref="I49:L49">
     <cfRule type="colorScale" priority="110">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12614,7 +12608,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I49:L49">
+  <conditionalFormatting sqref="I50:L50">
     <cfRule type="colorScale" priority="112">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12636,7 +12630,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I50:L50">
+  <conditionalFormatting sqref="I51:L51">
     <cfRule type="colorScale" priority="114">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12658,7 +12652,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I51:L51">
+  <conditionalFormatting sqref="I52:L52">
     <cfRule type="colorScale" priority="116">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12680,7 +12674,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I52:L52">
+  <conditionalFormatting sqref="I53:L53">
     <cfRule type="colorScale" priority="118">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12702,7 +12696,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I53:L53">
+  <conditionalFormatting sqref="I54:L54">
     <cfRule type="colorScale" priority="120">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12724,7 +12718,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I54:L54">
+  <conditionalFormatting sqref="I55:L55">
     <cfRule type="colorScale" priority="122">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12746,7 +12740,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I55:L55">
+  <conditionalFormatting sqref="I56:L56">
     <cfRule type="colorScale" priority="124">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12768,7 +12762,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I56:L56">
+  <conditionalFormatting sqref="I57:L57">
     <cfRule type="colorScale" priority="126">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12790,7 +12784,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I57:L57">
+  <conditionalFormatting sqref="I58:L58">
     <cfRule type="colorScale" priority="128">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12812,7 +12806,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I58:L58">
+  <conditionalFormatting sqref="I59:L59">
     <cfRule type="colorScale" priority="130">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12834,7 +12828,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I59:L59">
+  <conditionalFormatting sqref="I60:L60">
     <cfRule type="colorScale" priority="132">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12856,7 +12850,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I60:L60">
+  <conditionalFormatting sqref="I61:L61">
     <cfRule type="colorScale" priority="134">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12878,7 +12872,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I61:L61">
+  <conditionalFormatting sqref="I62:L62">
     <cfRule type="colorScale" priority="136">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12900,7 +12894,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I62:L62">
+  <conditionalFormatting sqref="I63:L63">
     <cfRule type="colorScale" priority="138">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12922,7 +12916,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I63:L63">
+  <conditionalFormatting sqref="I64:L64">
     <cfRule type="colorScale" priority="140">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12944,7 +12938,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I64:L64">
+  <conditionalFormatting sqref="I65:L65">
     <cfRule type="colorScale" priority="142">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12966,7 +12960,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I65:L65">
+  <conditionalFormatting sqref="I66:L66">
     <cfRule type="colorScale" priority="144">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12988,7 +12982,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I66:L66">
+  <conditionalFormatting sqref="I67:L67">
     <cfRule type="colorScale" priority="146">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13010,7 +13004,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I67:L67">
+  <conditionalFormatting sqref="I68:L68">
     <cfRule type="colorScale" priority="148">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13032,7 +13026,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I68:L68">
+  <conditionalFormatting sqref="I69:L69">
     <cfRule type="colorScale" priority="150">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13054,7 +13048,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I69:L69">
+  <conditionalFormatting sqref="I70:L70">
     <cfRule type="colorScale" priority="152">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13076,7 +13070,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I70:L70">
+  <conditionalFormatting sqref="I71:L71">
     <cfRule type="colorScale" priority="154">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13098,7 +13092,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I71:L71">
+  <conditionalFormatting sqref="I72:L72">
     <cfRule type="colorScale" priority="156">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13120,7 +13114,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I72:L72">
+  <conditionalFormatting sqref="I73:L73">
     <cfRule type="colorScale" priority="158">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13142,7 +13136,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I73:L73">
+  <conditionalFormatting sqref="I74:L74">
     <cfRule type="colorScale" priority="160">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13164,7 +13158,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I74:L74">
+  <conditionalFormatting sqref="I75:L75">
     <cfRule type="colorScale" priority="162">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13186,7 +13180,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I75:L75">
+  <conditionalFormatting sqref="I76:L76">
     <cfRule type="colorScale" priority="164">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13208,7 +13202,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I76:L76">
+  <conditionalFormatting sqref="I77:L77">
     <cfRule type="colorScale" priority="166">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13230,7 +13224,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I77:L77">
+  <conditionalFormatting sqref="I78:L78">
     <cfRule type="colorScale" priority="168">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13252,7 +13246,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I78:L78">
+  <conditionalFormatting sqref="I79:L79">
     <cfRule type="colorScale" priority="170">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13274,7 +13268,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I79:L79">
+  <conditionalFormatting sqref="I80:L80">
     <cfRule type="colorScale" priority="172">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13296,7 +13290,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I80:L80">
+  <conditionalFormatting sqref="I81:L81">
     <cfRule type="colorScale" priority="174">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13318,7 +13312,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I81:L81">
+  <conditionalFormatting sqref="I82:L82">
     <cfRule type="colorScale" priority="176">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13340,7 +13334,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I82:L82">
+  <conditionalFormatting sqref="I83:L83">
     <cfRule type="colorScale" priority="178">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13362,7 +13356,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I83:L83">
+  <conditionalFormatting sqref="I84:L84">
     <cfRule type="colorScale" priority="180">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13384,7 +13378,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I84:L84">
+  <conditionalFormatting sqref="I85:L85">
     <cfRule type="colorScale" priority="182">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13406,7 +13400,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I85:L85">
+  <conditionalFormatting sqref="I86:L86">
     <cfRule type="colorScale" priority="184">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13428,7 +13422,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I86:L86">
+  <conditionalFormatting sqref="I87:L87">
     <cfRule type="colorScale" priority="186">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13450,7 +13444,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I87:L87">
+  <conditionalFormatting sqref="I88:L88">
     <cfRule type="colorScale" priority="188">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13472,7 +13466,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I88:L88">
+  <conditionalFormatting sqref="I89:L89">
     <cfRule type="colorScale" priority="190">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13494,7 +13488,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I89:L89">
+  <conditionalFormatting sqref="I90:L90">
     <cfRule type="colorScale" priority="192">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13516,7 +13510,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I90:L90">
+  <conditionalFormatting sqref="I91:L91">
     <cfRule type="colorScale" priority="194">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13538,7 +13532,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I91:L91">
+  <conditionalFormatting sqref="I92:L92">
     <cfRule type="colorScale" priority="196">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13560,7 +13554,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I92:L92">
+  <conditionalFormatting sqref="I93:L93">
     <cfRule type="colorScale" priority="198">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13582,7 +13576,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I93:L93">
+  <conditionalFormatting sqref="I94:L94">
     <cfRule type="colorScale" priority="200">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13604,7 +13598,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I94:L94">
+  <conditionalFormatting sqref="I95:L95">
     <cfRule type="colorScale" priority="202">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13626,7 +13620,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I95:L95">
+  <conditionalFormatting sqref="I96:L96">
     <cfRule type="colorScale" priority="204">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13648,7 +13642,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I96:L96">
+  <conditionalFormatting sqref="I97:L97">
     <cfRule type="colorScale" priority="206">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13670,7 +13664,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I97:L97">
+  <conditionalFormatting sqref="I98:L98">
     <cfRule type="colorScale" priority="208">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13692,7 +13686,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I98:L98">
+  <conditionalFormatting sqref="I99:L99">
     <cfRule type="colorScale" priority="210">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13714,7 +13708,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I99:L99">
+  <conditionalFormatting sqref="I100:L100">
     <cfRule type="colorScale" priority="212">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13736,7 +13730,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I100:L100">
+  <conditionalFormatting sqref="I101:L101">
     <cfRule type="colorScale" priority="214">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13758,7 +13752,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I101:L101">
+  <conditionalFormatting sqref="I102:L102">
     <cfRule type="colorScale" priority="216">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13780,7 +13774,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I102:L102">
+  <conditionalFormatting sqref="I103:L103">
     <cfRule type="colorScale" priority="218">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13802,7 +13796,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I103:L103">
+  <conditionalFormatting sqref="I104:L104">
     <cfRule type="colorScale" priority="220">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13824,7 +13818,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I104:L104">
+  <conditionalFormatting sqref="I105:L105">
     <cfRule type="colorScale" priority="222">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13846,7 +13840,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I105:L105">
+  <conditionalFormatting sqref="I106:L106">
     <cfRule type="colorScale" priority="224">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13868,7 +13862,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I106:L106">
+  <conditionalFormatting sqref="I107:L107">
     <cfRule type="colorScale" priority="226">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13890,7 +13884,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I107:L107">
+  <conditionalFormatting sqref="I108:L108">
     <cfRule type="colorScale" priority="228">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13912,7 +13906,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I108:L108">
+  <conditionalFormatting sqref="I109:L109">
     <cfRule type="colorScale" priority="230">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13934,7 +13928,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I109:L109">
+  <conditionalFormatting sqref="I110:L110">
     <cfRule type="colorScale" priority="232">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13956,7 +13950,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I110:L110">
+  <conditionalFormatting sqref="I111:L111">
     <cfRule type="colorScale" priority="234">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -13978,7 +13972,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I111:L111">
+  <conditionalFormatting sqref="I112:L112">
     <cfRule type="colorScale" priority="236">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14000,7 +13994,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I112:L112">
+  <conditionalFormatting sqref="I113:L113">
     <cfRule type="colorScale" priority="238">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14022,7 +14016,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I113:L113">
+  <conditionalFormatting sqref="I114:L114">
     <cfRule type="colorScale" priority="240">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14044,7 +14038,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I114:L114">
+  <conditionalFormatting sqref="I115:L115">
     <cfRule type="colorScale" priority="242">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14066,7 +14060,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I115:L115">
+  <conditionalFormatting sqref="I116:L116">
     <cfRule type="colorScale" priority="244">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14088,7 +14082,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I116:L116">
+  <conditionalFormatting sqref="I117:L117">
     <cfRule type="colorScale" priority="246">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14110,7 +14104,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I117:L117">
+  <conditionalFormatting sqref="I118:L118">
     <cfRule type="colorScale" priority="248">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14132,7 +14126,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I118:L118">
+  <conditionalFormatting sqref="I119:L119">
     <cfRule type="colorScale" priority="250">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14154,7 +14148,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I119:L119">
+  <conditionalFormatting sqref="I120:L120">
     <cfRule type="colorScale" priority="252">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14176,7 +14170,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I120:L120">
+  <conditionalFormatting sqref="I121:L121">
     <cfRule type="colorScale" priority="254">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14198,7 +14192,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I121:L121">
+  <conditionalFormatting sqref="I122:L122">
     <cfRule type="colorScale" priority="256">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14220,7 +14214,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I122:L122">
+  <conditionalFormatting sqref="I123:L123">
     <cfRule type="colorScale" priority="258">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14242,7 +14236,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I123:L123">
+  <conditionalFormatting sqref="I124:L124">
     <cfRule type="colorScale" priority="260">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14264,7 +14258,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I124:L124">
+  <conditionalFormatting sqref="I125:L125">
     <cfRule type="colorScale" priority="262">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14286,7 +14280,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I125:L125">
+  <conditionalFormatting sqref="I126:L126">
     <cfRule type="colorScale" priority="264">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14308,7 +14302,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I126:L126">
+  <conditionalFormatting sqref="I127:L127">
     <cfRule type="colorScale" priority="266">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14330,7 +14324,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I127:L127">
+  <conditionalFormatting sqref="I128:L128">
     <cfRule type="colorScale" priority="268">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14352,7 +14346,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I128:L128">
+  <conditionalFormatting sqref="I129:L130">
     <cfRule type="colorScale" priority="270">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14374,7 +14368,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I129:L130">
+  <conditionalFormatting sqref="I131:L131">
     <cfRule type="colorScale" priority="272">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14396,7 +14390,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I131:L131">
+  <conditionalFormatting sqref="I132:L132">
     <cfRule type="colorScale" priority="274">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14418,7 +14412,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I132:L132">
+  <conditionalFormatting sqref="I133:L133">
     <cfRule type="colorScale" priority="276">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14440,7 +14434,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I133:L133">
+  <conditionalFormatting sqref="I134:L134">
     <cfRule type="colorScale" priority="278">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14462,7 +14456,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I134:L134">
+  <conditionalFormatting sqref="I135:L135">
     <cfRule type="colorScale" priority="280">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14484,7 +14478,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I135:L135">
+  <conditionalFormatting sqref="I136:L136">
     <cfRule type="colorScale" priority="282">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14495,6 +14489,8 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I137:L137">
     <cfRule type="colorScale" priority="283">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14505,8 +14501,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I136:L136">
     <cfRule type="colorScale" priority="284">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14518,7 +14512,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I137:L137">
+  <conditionalFormatting sqref="I138:L138">
     <cfRule type="colorScale" priority="285">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14540,7 +14534,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I138:L138">
+  <conditionalFormatting sqref="I139:L139">
     <cfRule type="colorScale" priority="287">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14562,7 +14556,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I139:L139">
+  <conditionalFormatting sqref="I140:L140">
     <cfRule type="colorScale" priority="289">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14584,7 +14578,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I140:L140">
+  <conditionalFormatting sqref="I141:L141">
     <cfRule type="colorScale" priority="291">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14606,7 +14600,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I141:L141">
+  <conditionalFormatting sqref="I142:L142">
     <cfRule type="colorScale" priority="293">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14628,7 +14622,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I142:L142">
+  <conditionalFormatting sqref="I143:L143">
     <cfRule type="colorScale" priority="295">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14650,7 +14644,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I143:L143">
+  <conditionalFormatting sqref="I144:L144">
     <cfRule type="colorScale" priority="297">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14672,7 +14666,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I144:L144">
+  <conditionalFormatting sqref="I145:L145">
     <cfRule type="colorScale" priority="299">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14694,7 +14688,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I145:L145">
+  <conditionalFormatting sqref="I146:L146">
     <cfRule type="colorScale" priority="301">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14716,7 +14710,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I146:L146">
+  <conditionalFormatting sqref="I147:L147">
     <cfRule type="colorScale" priority="303">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14738,7 +14732,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I147:L147">
+  <conditionalFormatting sqref="I148:L148">
     <cfRule type="colorScale" priority="305">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14760,7 +14754,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I148:L148">
+  <conditionalFormatting sqref="I149:L149">
     <cfRule type="colorScale" priority="307">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14782,7 +14776,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I149:L149">
+  <conditionalFormatting sqref="I150:L150">
     <cfRule type="colorScale" priority="309">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14804,7 +14798,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I150:L150">
+  <conditionalFormatting sqref="I151:L151">
     <cfRule type="colorScale" priority="311">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14826,7 +14820,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I151:L151">
+  <conditionalFormatting sqref="I152:L152">
     <cfRule type="colorScale" priority="313">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14848,7 +14842,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I152:L152">
+  <conditionalFormatting sqref="I153:L153">
     <cfRule type="colorScale" priority="315">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14870,7 +14864,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I153:L153">
+  <conditionalFormatting sqref="I154:L154">
     <cfRule type="colorScale" priority="317">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14892,7 +14886,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I154:L154">
+  <conditionalFormatting sqref="I155:L155">
     <cfRule type="colorScale" priority="319">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14914,7 +14908,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I155:L155">
+  <conditionalFormatting sqref="I156:L156">
     <cfRule type="colorScale" priority="321">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14936,7 +14930,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I156:L156">
+  <conditionalFormatting sqref="I157:L157">
     <cfRule type="colorScale" priority="323">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14958,7 +14952,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I157:L157">
+  <conditionalFormatting sqref="I158:L158">
     <cfRule type="colorScale" priority="325">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -14980,7 +14974,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I158:L158">
+  <conditionalFormatting sqref="I159:L159">
     <cfRule type="colorScale" priority="327">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15002,7 +14996,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I159:L159">
+  <conditionalFormatting sqref="I160:L160">
     <cfRule type="colorScale" priority="329">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15024,7 +15018,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I160:L160">
+  <conditionalFormatting sqref="I161:L161">
     <cfRule type="colorScale" priority="331">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15046,7 +15040,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I161:L161">
+  <conditionalFormatting sqref="I162:L162">
     <cfRule type="colorScale" priority="333">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15068,7 +15062,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I162:L162">
+  <conditionalFormatting sqref="I163:L163">
     <cfRule type="colorScale" priority="335">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15090,7 +15084,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I163:L163">
+  <conditionalFormatting sqref="I164:L164">
     <cfRule type="colorScale" priority="337">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15112,7 +15106,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I164:L164">
+  <conditionalFormatting sqref="I165:L165">
     <cfRule type="colorScale" priority="339">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15134,7 +15128,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I165:L165">
+  <conditionalFormatting sqref="I166:L166">
     <cfRule type="colorScale" priority="341">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15156,7 +15150,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I166:L166">
+  <conditionalFormatting sqref="I167:L167">
     <cfRule type="colorScale" priority="343">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15178,7 +15172,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I167:L167">
+  <conditionalFormatting sqref="I168:L168">
     <cfRule type="colorScale" priority="345">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15200,7 +15194,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I168:L168">
+  <conditionalFormatting sqref="I169:L169">
     <cfRule type="colorScale" priority="347">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15222,7 +15216,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I169:L169">
+  <conditionalFormatting sqref="I170:L170">
     <cfRule type="colorScale" priority="349">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15244,7 +15238,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I170:L170">
+  <conditionalFormatting sqref="I171:L171">
     <cfRule type="colorScale" priority="351">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15266,7 +15260,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I171:L171">
+  <conditionalFormatting sqref="I172:L172">
     <cfRule type="colorScale" priority="353">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15288,7 +15282,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I172:L172">
+  <conditionalFormatting sqref="I173:L173">
     <cfRule type="colorScale" priority="355">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15310,7 +15304,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I173:L173">
+  <conditionalFormatting sqref="I174:L174">
     <cfRule type="colorScale" priority="357">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15332,7 +15326,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I174:L174">
+  <conditionalFormatting sqref="I175:L175">
     <cfRule type="colorScale" priority="359">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15354,7 +15348,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I175:L175">
+  <conditionalFormatting sqref="I176:L176">
     <cfRule type="colorScale" priority="361">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15376,7 +15370,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I176:L176">
+  <conditionalFormatting sqref="I177:L177">
     <cfRule type="colorScale" priority="363">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15398,7 +15392,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I177:L177">
+  <conditionalFormatting sqref="I178:L178">
     <cfRule type="colorScale" priority="365">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15420,7 +15414,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I178:L178">
+  <conditionalFormatting sqref="I179:L179">
     <cfRule type="colorScale" priority="367">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15442,7 +15436,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I179:L179">
+  <conditionalFormatting sqref="I180:L180">
     <cfRule type="colorScale" priority="369">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15464,7 +15458,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I180:L180">
+  <conditionalFormatting sqref="I181:L181">
     <cfRule type="colorScale" priority="371">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15486,7 +15480,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I181:L181">
+  <conditionalFormatting sqref="I182:L182">
     <cfRule type="colorScale" priority="373">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15508,7 +15502,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I182:L182">
+  <conditionalFormatting sqref="I183:L183">
     <cfRule type="colorScale" priority="375">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15530,7 +15524,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I183:L183">
+  <conditionalFormatting sqref="I184:L184">
     <cfRule type="colorScale" priority="377">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15552,7 +15546,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I184:L184">
+  <conditionalFormatting sqref="I185:L185">
     <cfRule type="colorScale" priority="379">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15574,7 +15568,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I185:L185">
+  <conditionalFormatting sqref="I186:L186">
     <cfRule type="colorScale" priority="381">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15596,7 +15590,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I186:L186">
+  <conditionalFormatting sqref="I187:L187">
     <cfRule type="colorScale" priority="383">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15618,7 +15612,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I187:L187">
+  <conditionalFormatting sqref="I188:L188">
     <cfRule type="colorScale" priority="385">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15640,7 +15634,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I188:L188">
+  <conditionalFormatting sqref="I189:L189">
     <cfRule type="colorScale" priority="387">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15662,7 +15656,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I189:L189">
+  <conditionalFormatting sqref="I190:L190">
     <cfRule type="colorScale" priority="389">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15684,7 +15678,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I190:L190">
+  <conditionalFormatting sqref="I191:L191">
     <cfRule type="colorScale" priority="391">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15706,7 +15700,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I191:L191">
+  <conditionalFormatting sqref="I192:L192">
     <cfRule type="colorScale" priority="393">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15728,7 +15722,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I192:L192">
+  <conditionalFormatting sqref="I193:L193">
     <cfRule type="colorScale" priority="395">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15750,7 +15744,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I193:L193">
+  <conditionalFormatting sqref="I194:L194">
     <cfRule type="colorScale" priority="397">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15772,7 +15766,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I194:L194">
+  <conditionalFormatting sqref="I195:L195">
     <cfRule type="colorScale" priority="399">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15794,7 +15788,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I195:L195">
+  <conditionalFormatting sqref="I196:L196">
     <cfRule type="colorScale" priority="401">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15816,7 +15810,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I196:L196">
+  <conditionalFormatting sqref="I197:L197">
     <cfRule type="colorScale" priority="403">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15838,7 +15832,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I197:L197">
+  <conditionalFormatting sqref="I198:L198">
     <cfRule type="colorScale" priority="405">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15860,7 +15854,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I198:L198">
+  <conditionalFormatting sqref="I199:L199">
     <cfRule type="colorScale" priority="407">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15882,7 +15876,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I199:L199">
+  <conditionalFormatting sqref="I200:L200">
     <cfRule type="colorScale" priority="409">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15904,7 +15898,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I200:L200">
+  <conditionalFormatting sqref="I201:L201">
     <cfRule type="colorScale" priority="411">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15926,7 +15920,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I201:L201">
+  <conditionalFormatting sqref="I202:L202">
     <cfRule type="colorScale" priority="413">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15948,7 +15942,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I202:L202">
+  <conditionalFormatting sqref="I203:L203">
     <cfRule type="colorScale" priority="415">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15970,7 +15964,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I203:L203">
+  <conditionalFormatting sqref="I204:L204">
     <cfRule type="colorScale" priority="417">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -15992,7 +15986,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I204:L204">
+  <conditionalFormatting sqref="I205:L205">
     <cfRule type="colorScale" priority="419">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16014,7 +16008,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I205:L205">
+  <conditionalFormatting sqref="I206:L206">
     <cfRule type="colorScale" priority="421">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16036,7 +16030,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I206:L206">
+  <conditionalFormatting sqref="I207:L207">
     <cfRule type="colorScale" priority="423">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16058,7 +16052,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I207:L207">
+  <conditionalFormatting sqref="I208:L208">
     <cfRule type="colorScale" priority="425">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16080,7 +16074,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I208:L208">
+  <conditionalFormatting sqref="I209:L209">
     <cfRule type="colorScale" priority="427">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16102,7 +16096,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I209:L209">
+  <conditionalFormatting sqref="I210:L210">
     <cfRule type="colorScale" priority="429">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16124,7 +16118,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I210:L210">
+  <conditionalFormatting sqref="I211:L211">
     <cfRule type="colorScale" priority="431">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16146,7 +16140,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I211:L211">
+  <conditionalFormatting sqref="I212:L212">
     <cfRule type="colorScale" priority="433">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16168,7 +16162,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I212:L212">
+  <conditionalFormatting sqref="I213:L213">
     <cfRule type="colorScale" priority="435">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16190,7 +16184,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I213:L213">
+  <conditionalFormatting sqref="I214:L215">
     <cfRule type="colorScale" priority="437">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16212,7 +16206,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I214:L215">
+  <conditionalFormatting sqref="I217:L217">
     <cfRule type="colorScale" priority="439">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16234,7 +16228,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I217:L217">
+  <conditionalFormatting sqref="I218:L219">
     <cfRule type="colorScale" priority="441">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16256,7 +16250,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I218:L219">
+  <conditionalFormatting sqref="I220:L221">
     <cfRule type="colorScale" priority="443">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16278,7 +16272,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I220:L221">
+  <conditionalFormatting sqref="I222:L223">
     <cfRule type="colorScale" priority="445">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16300,7 +16294,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I222:L223">
+  <conditionalFormatting sqref="I224:L224">
     <cfRule type="colorScale" priority="447">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16322,7 +16316,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I224:L224">
+  <conditionalFormatting sqref="I225:L225">
     <cfRule type="colorScale" priority="449">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16344,7 +16338,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I225:L225">
+  <conditionalFormatting sqref="I226:L226">
     <cfRule type="colorScale" priority="451">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16366,7 +16360,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I226:L226">
+  <conditionalFormatting sqref="I228:L231">
     <cfRule type="colorScale" priority="453">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16388,7 +16382,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I227:L227">
+  <conditionalFormatting sqref="I232">
     <cfRule type="colorScale" priority="455">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16410,7 +16404,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I228:L231">
+  <conditionalFormatting sqref="I233">
     <cfRule type="colorScale" priority="457">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16432,7 +16426,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I232">
+  <conditionalFormatting sqref="I234:L235">
     <cfRule type="colorScale" priority="459">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16454,7 +16448,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I233">
+  <conditionalFormatting sqref="I236:L236">
     <cfRule type="colorScale" priority="461">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16476,7 +16470,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I234:L235">
+  <conditionalFormatting sqref="I237 I238:L238">
     <cfRule type="colorScale" priority="463">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16498,7 +16492,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I236:L236">
+  <conditionalFormatting sqref="G2">
     <cfRule type="colorScale" priority="465">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16520,7 +16514,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I237 I238:L238">
+  <conditionalFormatting sqref="G3 G5">
     <cfRule type="colorScale" priority="467">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16542,7 +16536,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
+  <conditionalFormatting sqref="G6">
     <cfRule type="colorScale" priority="469">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16564,7 +16558,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3 G5">
+  <conditionalFormatting sqref="G7">
     <cfRule type="colorScale" priority="471">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16586,7 +16580,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
+  <conditionalFormatting sqref="G8">
     <cfRule type="colorScale" priority="473">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16608,7 +16602,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7">
+  <conditionalFormatting sqref="G9">
     <cfRule type="colorScale" priority="475">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16630,7 +16624,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
+  <conditionalFormatting sqref="G10">
     <cfRule type="colorScale" priority="477">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16652,7 +16646,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G9">
+  <conditionalFormatting sqref="G11">
     <cfRule type="colorScale" priority="479">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16674,7 +16668,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G10">
+  <conditionalFormatting sqref="G12">
     <cfRule type="colorScale" priority="481">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16696,7 +16690,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G11">
+  <conditionalFormatting sqref="G13">
     <cfRule type="colorScale" priority="483">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16718,7 +16712,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G12">
+  <conditionalFormatting sqref="G14">
     <cfRule type="colorScale" priority="485">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16740,7 +16734,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G13">
+  <conditionalFormatting sqref="G15">
     <cfRule type="colorScale" priority="487">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16762,7 +16756,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14">
+  <conditionalFormatting sqref="G16">
     <cfRule type="colorScale" priority="489">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16784,7 +16778,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G15">
+  <conditionalFormatting sqref="G17">
     <cfRule type="colorScale" priority="491">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16806,7 +16800,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G16">
+  <conditionalFormatting sqref="G18">
     <cfRule type="colorScale" priority="493">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16828,7 +16822,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G17">
+  <conditionalFormatting sqref="G19">
     <cfRule type="colorScale" priority="495">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16850,7 +16844,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G18">
+  <conditionalFormatting sqref="G20">
     <cfRule type="colorScale" priority="497">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16872,7 +16866,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G19">
+  <conditionalFormatting sqref="G21">
     <cfRule type="colorScale" priority="499">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16894,7 +16888,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G20">
+  <conditionalFormatting sqref="G22">
     <cfRule type="colorScale" priority="501">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16916,7 +16910,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G21">
+  <conditionalFormatting sqref="G23">
     <cfRule type="colorScale" priority="503">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16938,7 +16932,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G22">
+  <conditionalFormatting sqref="G26">
     <cfRule type="colorScale" priority="505">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16960,7 +16954,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23">
+  <conditionalFormatting sqref="G27">
     <cfRule type="colorScale" priority="507">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -16982,7 +16976,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G26">
+  <conditionalFormatting sqref="G28">
     <cfRule type="colorScale" priority="509">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17004,7 +16998,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G27">
+  <conditionalFormatting sqref="G29">
     <cfRule type="colorScale" priority="511">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17026,7 +17020,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G28">
+  <conditionalFormatting sqref="G30">
     <cfRule type="colorScale" priority="513">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17048,7 +17042,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G29">
+  <conditionalFormatting sqref="G31">
     <cfRule type="colorScale" priority="515">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17070,7 +17064,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G30">
+  <conditionalFormatting sqref="G32">
     <cfRule type="colorScale" priority="517">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17092,7 +17086,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G31">
+  <conditionalFormatting sqref="G33">
     <cfRule type="colorScale" priority="519">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17114,7 +17108,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G32">
+  <conditionalFormatting sqref="G34">
     <cfRule type="colorScale" priority="521">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17136,7 +17130,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G33">
+  <conditionalFormatting sqref="G35">
     <cfRule type="colorScale" priority="523">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17158,7 +17152,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G34">
+  <conditionalFormatting sqref="G36">
     <cfRule type="colorScale" priority="525">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17180,7 +17174,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G35">
+  <conditionalFormatting sqref="G37">
     <cfRule type="colorScale" priority="527">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17202,7 +17196,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G36">
+  <conditionalFormatting sqref="G38">
     <cfRule type="colorScale" priority="529">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17224,7 +17218,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G37">
+  <conditionalFormatting sqref="G39">
     <cfRule type="colorScale" priority="531">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17246,7 +17240,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G38">
+  <conditionalFormatting sqref="G40">
     <cfRule type="colorScale" priority="533">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17268,7 +17262,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G39">
+  <conditionalFormatting sqref="G41">
     <cfRule type="colorScale" priority="535">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17290,7 +17284,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G40">
+  <conditionalFormatting sqref="G42">
     <cfRule type="colorScale" priority="537">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17312,7 +17306,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G41">
+  <conditionalFormatting sqref="G43">
     <cfRule type="colorScale" priority="539">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17334,7 +17328,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G42">
+  <conditionalFormatting sqref="G44">
     <cfRule type="colorScale" priority="541">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17356,7 +17350,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G43">
+  <conditionalFormatting sqref="G45">
     <cfRule type="colorScale" priority="543">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17378,7 +17372,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G44">
+  <conditionalFormatting sqref="G46">
     <cfRule type="colorScale" priority="545">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17400,7 +17394,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G45">
+  <conditionalFormatting sqref="G47">
     <cfRule type="colorScale" priority="547">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17422,7 +17416,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G46">
+  <conditionalFormatting sqref="G48">
     <cfRule type="colorScale" priority="549">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17444,7 +17438,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G47">
+  <conditionalFormatting sqref="G49">
     <cfRule type="colorScale" priority="551">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17466,7 +17460,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G48">
+  <conditionalFormatting sqref="G50">
     <cfRule type="colorScale" priority="553">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17488,7 +17482,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G49">
+  <conditionalFormatting sqref="G51">
     <cfRule type="colorScale" priority="555">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17510,7 +17504,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G50">
+  <conditionalFormatting sqref="G52">
     <cfRule type="colorScale" priority="557">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17532,7 +17526,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G51">
+  <conditionalFormatting sqref="G53">
     <cfRule type="colorScale" priority="559">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17554,7 +17548,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G52">
+  <conditionalFormatting sqref="G54">
     <cfRule type="colorScale" priority="561">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17576,7 +17570,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G53">
+  <conditionalFormatting sqref="G55">
     <cfRule type="colorScale" priority="563">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17598,7 +17592,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G54">
+  <conditionalFormatting sqref="G56">
     <cfRule type="colorScale" priority="565">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17620,7 +17614,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G55">
+  <conditionalFormatting sqref="G57">
     <cfRule type="colorScale" priority="567">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17642,7 +17636,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G56">
+  <conditionalFormatting sqref="G58">
     <cfRule type="colorScale" priority="569">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17664,7 +17658,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G57">
+  <conditionalFormatting sqref="G59">
     <cfRule type="colorScale" priority="571">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17686,7 +17680,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G58">
+  <conditionalFormatting sqref="G60">
     <cfRule type="colorScale" priority="573">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17708,7 +17702,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G59">
+  <conditionalFormatting sqref="G61">
     <cfRule type="colorScale" priority="575">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17730,7 +17724,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G60">
+  <conditionalFormatting sqref="G62">
     <cfRule type="colorScale" priority="577">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17752,7 +17746,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G61">
+  <conditionalFormatting sqref="G63">
     <cfRule type="colorScale" priority="579">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17774,7 +17768,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G62">
+  <conditionalFormatting sqref="G64">
     <cfRule type="colorScale" priority="581">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17796,7 +17790,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G63">
+  <conditionalFormatting sqref="G65">
     <cfRule type="colorScale" priority="583">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17818,7 +17812,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G64">
+  <conditionalFormatting sqref="G66">
     <cfRule type="colorScale" priority="585">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17840,7 +17834,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G65">
+  <conditionalFormatting sqref="G67">
     <cfRule type="colorScale" priority="587">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17862,7 +17856,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G66">
+  <conditionalFormatting sqref="G68">
     <cfRule type="colorScale" priority="589">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17884,7 +17878,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G67">
+  <conditionalFormatting sqref="G69">
     <cfRule type="colorScale" priority="591">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17906,7 +17900,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G68">
+  <conditionalFormatting sqref="G70">
     <cfRule type="colorScale" priority="593">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17928,7 +17922,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G69">
+  <conditionalFormatting sqref="G71">
     <cfRule type="colorScale" priority="595">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17950,7 +17944,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G70">
+  <conditionalFormatting sqref="G72">
     <cfRule type="colorScale" priority="597">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17972,7 +17966,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G71">
+  <conditionalFormatting sqref="G73">
     <cfRule type="colorScale" priority="599">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17994,7 +17988,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G72">
+  <conditionalFormatting sqref="G74">
     <cfRule type="colorScale" priority="601">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18016,7 +18010,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G73">
+  <conditionalFormatting sqref="G75">
     <cfRule type="colorScale" priority="603">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18038,7 +18032,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G74">
+  <conditionalFormatting sqref="G76">
     <cfRule type="colorScale" priority="605">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18060,7 +18054,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G75">
+  <conditionalFormatting sqref="G77">
     <cfRule type="colorScale" priority="607">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18082,7 +18076,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G76">
+  <conditionalFormatting sqref="G78">
     <cfRule type="colorScale" priority="609">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18104,7 +18098,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G77">
+  <conditionalFormatting sqref="G79">
     <cfRule type="colorScale" priority="611">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18126,7 +18120,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G78">
+  <conditionalFormatting sqref="G80">
     <cfRule type="colorScale" priority="613">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18148,7 +18142,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G79">
+  <conditionalFormatting sqref="G81">
     <cfRule type="colorScale" priority="615">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18170,7 +18164,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G80">
+  <conditionalFormatting sqref="G82">
     <cfRule type="colorScale" priority="617">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18192,7 +18186,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G81">
+  <conditionalFormatting sqref="G83">
     <cfRule type="colorScale" priority="619">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18214,7 +18208,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G82">
+  <conditionalFormatting sqref="G84">
     <cfRule type="colorScale" priority="621">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18236,7 +18230,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G83">
+  <conditionalFormatting sqref="G85">
     <cfRule type="colorScale" priority="623">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18258,7 +18252,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G84">
+  <conditionalFormatting sqref="G86">
     <cfRule type="colorScale" priority="625">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18280,7 +18274,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G85">
+  <conditionalFormatting sqref="G87">
     <cfRule type="colorScale" priority="627">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18302,7 +18296,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G86">
+  <conditionalFormatting sqref="G88">
     <cfRule type="colorScale" priority="629">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18324,7 +18318,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G87">
+  <conditionalFormatting sqref="G89">
     <cfRule type="colorScale" priority="631">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18346,7 +18340,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G88">
+  <conditionalFormatting sqref="G90">
     <cfRule type="colorScale" priority="633">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18368,7 +18362,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G89">
+  <conditionalFormatting sqref="G91">
     <cfRule type="colorScale" priority="635">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18390,7 +18384,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G90">
+  <conditionalFormatting sqref="G92">
     <cfRule type="colorScale" priority="637">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18412,7 +18406,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G91">
+  <conditionalFormatting sqref="G93">
     <cfRule type="colorScale" priority="639">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18434,7 +18428,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G92">
+  <conditionalFormatting sqref="G94">
     <cfRule type="colorScale" priority="641">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18456,7 +18450,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G93">
+  <conditionalFormatting sqref="G95">
     <cfRule type="colorScale" priority="643">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18478,7 +18472,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G94">
+  <conditionalFormatting sqref="G96">
     <cfRule type="colorScale" priority="645">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18500,7 +18494,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G95">
+  <conditionalFormatting sqref="G97">
     <cfRule type="colorScale" priority="647">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18522,7 +18516,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G96">
+  <conditionalFormatting sqref="G98">
     <cfRule type="colorScale" priority="649">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18544,7 +18538,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G97">
+  <conditionalFormatting sqref="G99">
     <cfRule type="colorScale" priority="651">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18566,7 +18560,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G98">
+  <conditionalFormatting sqref="G100">
     <cfRule type="colorScale" priority="653">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18588,7 +18582,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G99">
+  <conditionalFormatting sqref="G101">
     <cfRule type="colorScale" priority="655">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18610,7 +18604,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G100">
+  <conditionalFormatting sqref="G102">
     <cfRule type="colorScale" priority="657">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18632,7 +18626,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G101">
+  <conditionalFormatting sqref="G103">
     <cfRule type="colorScale" priority="659">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18654,7 +18648,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G102">
+  <conditionalFormatting sqref="G104">
     <cfRule type="colorScale" priority="661">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18676,7 +18670,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G103">
+  <conditionalFormatting sqref="G105">
     <cfRule type="colorScale" priority="663">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18698,7 +18692,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G104">
+  <conditionalFormatting sqref="G106">
     <cfRule type="colorScale" priority="665">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18720,7 +18714,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G105">
+  <conditionalFormatting sqref="G107">
     <cfRule type="colorScale" priority="667">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18742,7 +18736,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G106">
+  <conditionalFormatting sqref="G108">
     <cfRule type="colorScale" priority="669">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18764,7 +18758,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G107">
+  <conditionalFormatting sqref="G109">
     <cfRule type="colorScale" priority="671">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18786,7 +18780,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G108">
+  <conditionalFormatting sqref="G110">
     <cfRule type="colorScale" priority="673">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18808,7 +18802,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G109">
+  <conditionalFormatting sqref="G111">
     <cfRule type="colorScale" priority="675">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18830,7 +18824,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G110">
+  <conditionalFormatting sqref="G112">
     <cfRule type="colorScale" priority="677">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18852,7 +18846,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G111">
+  <conditionalFormatting sqref="G113">
     <cfRule type="colorScale" priority="679">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18874,7 +18868,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G112">
+  <conditionalFormatting sqref="G114">
     <cfRule type="colorScale" priority="681">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18896,7 +18890,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G113">
+  <conditionalFormatting sqref="G115">
     <cfRule type="colorScale" priority="683">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18918,7 +18912,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G114">
+  <conditionalFormatting sqref="G116">
     <cfRule type="colorScale" priority="685">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18940,7 +18934,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G115">
+  <conditionalFormatting sqref="G117">
     <cfRule type="colorScale" priority="687">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18962,7 +18956,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G116">
+  <conditionalFormatting sqref="G118">
     <cfRule type="colorScale" priority="689">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -18984,7 +18978,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G117">
+  <conditionalFormatting sqref="G119">
     <cfRule type="colorScale" priority="691">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19006,7 +19000,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G118">
+  <conditionalFormatting sqref="G120">
     <cfRule type="colorScale" priority="693">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19028,7 +19022,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G119">
+  <conditionalFormatting sqref="G121">
     <cfRule type="colorScale" priority="695">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19050,7 +19044,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G120">
+  <conditionalFormatting sqref="G122">
     <cfRule type="colorScale" priority="697">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19072,7 +19066,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G121">
+  <conditionalFormatting sqref="G123">
     <cfRule type="colorScale" priority="699">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19094,7 +19088,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G122">
+  <conditionalFormatting sqref="G124">
     <cfRule type="colorScale" priority="701">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19116,7 +19110,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G123">
+  <conditionalFormatting sqref="G125">
     <cfRule type="colorScale" priority="703">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19138,7 +19132,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G124">
+  <conditionalFormatting sqref="G126">
     <cfRule type="colorScale" priority="705">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19160,7 +19154,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G125">
+  <conditionalFormatting sqref="G127">
     <cfRule type="colorScale" priority="707">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19182,7 +19176,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G126">
+  <conditionalFormatting sqref="G128">
     <cfRule type="colorScale" priority="709">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19204,7 +19198,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G127">
+  <conditionalFormatting sqref="G129:G130">
     <cfRule type="colorScale" priority="711">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19226,7 +19220,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G128">
+  <conditionalFormatting sqref="G131">
     <cfRule type="colorScale" priority="713">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19248,7 +19242,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G129:G130">
+  <conditionalFormatting sqref="G132">
     <cfRule type="colorScale" priority="715">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19270,7 +19264,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G131">
+  <conditionalFormatting sqref="G133">
     <cfRule type="colorScale" priority="717">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19292,7 +19286,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G132">
+  <conditionalFormatting sqref="G134">
     <cfRule type="colorScale" priority="719">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19314,7 +19308,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G133">
+  <conditionalFormatting sqref="G135">
     <cfRule type="colorScale" priority="721">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19336,7 +19330,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G134">
+  <conditionalFormatting sqref="G136">
     <cfRule type="colorScale" priority="723">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19358,7 +19352,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G135">
+  <conditionalFormatting sqref="G137">
     <cfRule type="colorScale" priority="725">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19380,7 +19374,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G136">
+  <conditionalFormatting sqref="G138">
     <cfRule type="colorScale" priority="727">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19402,7 +19396,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G137">
+  <conditionalFormatting sqref="G139">
     <cfRule type="colorScale" priority="729">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19424,7 +19418,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G138">
+  <conditionalFormatting sqref="G140">
     <cfRule type="colorScale" priority="731">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19446,7 +19440,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G139">
+  <conditionalFormatting sqref="G141">
     <cfRule type="colorScale" priority="733">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19468,7 +19462,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G140">
+  <conditionalFormatting sqref="G142">
     <cfRule type="colorScale" priority="735">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19490,7 +19484,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G141">
+  <conditionalFormatting sqref="G143">
     <cfRule type="colorScale" priority="737">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19512,7 +19506,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G142">
+  <conditionalFormatting sqref="G144">
     <cfRule type="colorScale" priority="739">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19534,7 +19528,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G143">
+  <conditionalFormatting sqref="G145">
     <cfRule type="colorScale" priority="741">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19556,7 +19550,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G144">
+  <conditionalFormatting sqref="G146">
     <cfRule type="colorScale" priority="743">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19578,7 +19572,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G145">
+  <conditionalFormatting sqref="G147">
     <cfRule type="colorScale" priority="745">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19600,7 +19594,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G146">
+  <conditionalFormatting sqref="G148">
     <cfRule type="colorScale" priority="747">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19622,7 +19616,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G147">
+  <conditionalFormatting sqref="G149">
     <cfRule type="colorScale" priority="749">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19644,7 +19638,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G148">
+  <conditionalFormatting sqref="G150">
     <cfRule type="colorScale" priority="751">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19666,7 +19660,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G149">
+  <conditionalFormatting sqref="G151">
     <cfRule type="colorScale" priority="753">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19688,7 +19682,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G150">
+  <conditionalFormatting sqref="G152">
     <cfRule type="colorScale" priority="755">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19710,7 +19704,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G151">
+  <conditionalFormatting sqref="G153">
     <cfRule type="colorScale" priority="757">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19732,7 +19726,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G152">
+  <conditionalFormatting sqref="G154">
     <cfRule type="colorScale" priority="759">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19754,7 +19748,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G153">
+  <conditionalFormatting sqref="G155">
     <cfRule type="colorScale" priority="761">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19776,7 +19770,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G154">
+  <conditionalFormatting sqref="G156">
     <cfRule type="colorScale" priority="763">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19798,7 +19792,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G155">
+  <conditionalFormatting sqref="G157">
     <cfRule type="colorScale" priority="765">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19820,7 +19814,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G156">
+  <conditionalFormatting sqref="G158">
     <cfRule type="colorScale" priority="767">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19842,7 +19836,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G157">
+  <conditionalFormatting sqref="G159">
     <cfRule type="colorScale" priority="769">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19864,7 +19858,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G158">
+  <conditionalFormatting sqref="G160">
     <cfRule type="colorScale" priority="771">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19886,7 +19880,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G159">
+  <conditionalFormatting sqref="G161">
     <cfRule type="colorScale" priority="773">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19908,7 +19902,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G160">
+  <conditionalFormatting sqref="G162">
     <cfRule type="colorScale" priority="775">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19930,7 +19924,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G161">
+  <conditionalFormatting sqref="G163">
     <cfRule type="colorScale" priority="777">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19952,7 +19946,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G162">
+  <conditionalFormatting sqref="G164">
     <cfRule type="colorScale" priority="779">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19974,7 +19968,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G163">
+  <conditionalFormatting sqref="G165">
     <cfRule type="colorScale" priority="781">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -19996,7 +19990,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G164">
+  <conditionalFormatting sqref="G166">
     <cfRule type="colorScale" priority="783">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20018,7 +20012,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G165">
+  <conditionalFormatting sqref="G167">
     <cfRule type="colorScale" priority="785">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20040,7 +20034,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G166">
+  <conditionalFormatting sqref="G168">
     <cfRule type="colorScale" priority="787">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20062,7 +20056,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G167">
+  <conditionalFormatting sqref="G169">
     <cfRule type="colorScale" priority="789">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20084,7 +20078,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G168">
+  <conditionalFormatting sqref="G170">
     <cfRule type="colorScale" priority="791">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20106,7 +20100,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G169">
+  <conditionalFormatting sqref="G171">
     <cfRule type="colorScale" priority="793">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20128,7 +20122,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G170">
+  <conditionalFormatting sqref="G172">
     <cfRule type="colorScale" priority="795">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20150,7 +20144,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G171">
+  <conditionalFormatting sqref="G173">
     <cfRule type="colorScale" priority="797">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20172,7 +20166,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G172">
+  <conditionalFormatting sqref="G174">
     <cfRule type="colorScale" priority="799">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20194,7 +20188,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G173">
+  <conditionalFormatting sqref="G175">
     <cfRule type="colorScale" priority="801">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20216,7 +20210,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G174">
+  <conditionalFormatting sqref="G176">
     <cfRule type="colorScale" priority="803">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20238,7 +20232,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G175">
+  <conditionalFormatting sqref="G177">
     <cfRule type="colorScale" priority="805">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20260,7 +20254,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G176">
+  <conditionalFormatting sqref="G178">
     <cfRule type="colorScale" priority="807">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20282,7 +20276,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G177">
+  <conditionalFormatting sqref="G179">
     <cfRule type="colorScale" priority="809">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20304,7 +20298,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G178">
+  <conditionalFormatting sqref="G180">
     <cfRule type="colorScale" priority="811">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20326,7 +20320,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G179">
+  <conditionalFormatting sqref="G181">
     <cfRule type="colorScale" priority="813">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20348,7 +20342,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G180">
+  <conditionalFormatting sqref="G182">
     <cfRule type="colorScale" priority="815">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20370,7 +20364,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G181">
+  <conditionalFormatting sqref="G183">
     <cfRule type="colorScale" priority="817">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20392,7 +20386,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G182">
+  <conditionalFormatting sqref="G184">
     <cfRule type="colorScale" priority="819">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20414,7 +20408,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G183">
+  <conditionalFormatting sqref="G185">
     <cfRule type="colorScale" priority="821">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20436,7 +20430,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G184">
+  <conditionalFormatting sqref="G186">
     <cfRule type="colorScale" priority="823">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20458,7 +20452,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G185">
+  <conditionalFormatting sqref="G187">
     <cfRule type="colorScale" priority="825">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20480,7 +20474,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G186">
+  <conditionalFormatting sqref="G188">
     <cfRule type="colorScale" priority="827">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20502,7 +20496,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G187">
+  <conditionalFormatting sqref="G189">
     <cfRule type="colorScale" priority="829">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20524,7 +20518,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G188">
+  <conditionalFormatting sqref="G190">
     <cfRule type="colorScale" priority="831">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20546,7 +20540,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G189">
+  <conditionalFormatting sqref="G191">
     <cfRule type="colorScale" priority="833">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20568,7 +20562,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G190">
+  <conditionalFormatting sqref="G192">
     <cfRule type="colorScale" priority="835">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20590,7 +20584,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G191">
+  <conditionalFormatting sqref="G193">
     <cfRule type="colorScale" priority="837">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20612,7 +20606,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G192">
+  <conditionalFormatting sqref="G194">
     <cfRule type="colorScale" priority="839">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20634,7 +20628,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G193">
+  <conditionalFormatting sqref="G195">
     <cfRule type="colorScale" priority="841">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20656,7 +20650,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G194">
+  <conditionalFormatting sqref="G196">
     <cfRule type="colorScale" priority="843">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20678,7 +20672,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G195">
+  <conditionalFormatting sqref="G197">
     <cfRule type="colorScale" priority="845">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20700,7 +20694,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G196">
+  <conditionalFormatting sqref="G198">
     <cfRule type="colorScale" priority="847">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20722,7 +20716,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G197">
+  <conditionalFormatting sqref="G199">
     <cfRule type="colorScale" priority="849">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20744,7 +20738,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G198">
+  <conditionalFormatting sqref="G200">
     <cfRule type="colorScale" priority="851">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20766,7 +20760,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G199">
+  <conditionalFormatting sqref="G201">
     <cfRule type="colorScale" priority="853">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20788,7 +20782,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G200">
+  <conditionalFormatting sqref="G202">
     <cfRule type="colorScale" priority="855">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20810,7 +20804,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G201">
+  <conditionalFormatting sqref="G203">
     <cfRule type="colorScale" priority="857">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20832,7 +20826,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G202">
+  <conditionalFormatting sqref="G204">
     <cfRule type="colorScale" priority="859">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20854,7 +20848,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G203">
+  <conditionalFormatting sqref="G205">
     <cfRule type="colorScale" priority="861">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20876,7 +20870,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G204">
+  <conditionalFormatting sqref="G206">
     <cfRule type="colorScale" priority="863">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20898,7 +20892,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G205">
+  <conditionalFormatting sqref="G207">
     <cfRule type="colorScale" priority="865">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20920,7 +20914,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G206">
+  <conditionalFormatting sqref="G208">
     <cfRule type="colorScale" priority="867">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20942,7 +20936,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G207">
+  <conditionalFormatting sqref="G209">
     <cfRule type="colorScale" priority="869">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20964,7 +20958,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G208">
+  <conditionalFormatting sqref="G210">
     <cfRule type="colorScale" priority="871">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -20986,7 +20980,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G209">
+  <conditionalFormatting sqref="G211">
     <cfRule type="colorScale" priority="873">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -21008,7 +21002,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G210">
+  <conditionalFormatting sqref="G212">
     <cfRule type="colorScale" priority="875">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -21030,7 +21024,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G211">
+  <conditionalFormatting sqref="G213">
     <cfRule type="colorScale" priority="877">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -21052,7 +21046,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G212">
+  <conditionalFormatting sqref="G215">
     <cfRule type="colorScale" priority="879">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -21074,7 +21068,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G213">
+  <conditionalFormatting sqref="G216:G217">
     <cfRule type="colorScale" priority="881">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -21096,7 +21090,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G215">
+  <conditionalFormatting sqref="G218:G221">
     <cfRule type="colorScale" priority="883">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -21118,7 +21112,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G216:G217">
+  <conditionalFormatting sqref="G222:G223">
     <cfRule type="colorScale" priority="885">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -21140,7 +21134,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G218:G221">
+  <conditionalFormatting sqref="G224:G225">
     <cfRule type="colorScale" priority="887">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -21162,7 +21156,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G222:G223">
+  <conditionalFormatting sqref="G237:G238">
     <cfRule type="colorScale" priority="889">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -21184,7 +21178,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G224:G225">
+  <conditionalFormatting sqref="G24:G25">
     <cfRule type="colorScale" priority="891">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -21206,7 +21200,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G237:G238">
+  <conditionalFormatting sqref="G214">
     <cfRule type="colorScale" priority="893">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -21228,7 +21222,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G24:G25">
+  <conditionalFormatting sqref="G228:G232">
     <cfRule type="colorScale" priority="895">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -21250,7 +21244,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G214">
+  <conditionalFormatting sqref="G234:G236">
     <cfRule type="colorScale" priority="897">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -21262,50 +21256,6 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="898">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G228:G232">
-    <cfRule type="colorScale" priority="899">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="900">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G234:G236">
-    <cfRule type="colorScale" priority="901">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="902">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -21340,18 +21290,18 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
@@ -21414,7 +21364,7 @@
         <v>159</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C7" s="2" t="str">
         <f aca="false">IF(ISNA(VLOOKUP(A7,$B$2:$B$170,1,FALSE())),A7,"")</f>
@@ -21651,7 +21601,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>105</v>
@@ -21663,7 +21613,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>107</v>
@@ -21675,7 +21625,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>110</v>
@@ -21687,7 +21637,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>112</v>
@@ -21843,7 +21793,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>161</v>
@@ -21855,7 +21805,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>163</v>
@@ -21867,7 +21817,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>168</v>
@@ -21879,7 +21829,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>173</v>
@@ -21903,7 +21853,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>181</v>
@@ -21915,7 +21865,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>184</v>
@@ -21927,7 +21877,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>175</v>
@@ -22134,7 +22084,7 @@
         <v>354</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C67" s="2" t="str">
         <f aca="false">IF(ISNA(VLOOKUP(A67,$B$2:$B$170,1,FALSE())),A67,"")</f>
@@ -22146,7 +22096,7 @@
         <v>357</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C68" s="2" t="str">
         <f aca="false">IF(ISNA(VLOOKUP(A68,$B$2:$B$170,1,FALSE())),A68,"")</f>
@@ -22158,7 +22108,7 @@
         <v>359</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C69" s="2" t="str">
         <f aca="false">IF(ISNA(VLOOKUP(A69,$B$2:$B$170,1,FALSE())),A69,"")</f>
@@ -22170,7 +22120,7 @@
         <v>361</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C70" s="2" t="str">
         <f aca="false">IF(ISNA(VLOOKUP(A70,$B$2:$B$170,1,FALSE())),A70,"")</f>
@@ -22275,7 +22225,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>318</v>
@@ -22686,7 +22636,7 @@
         <v>461</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C113" s="2" t="str">
         <f aca="false">IF(ISNA(VLOOKUP(A113,$B$2:$B$170,1,FALSE())),A113,"")</f>
@@ -22851,7 +22801,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>419</v>
@@ -22863,7 +22813,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>421</v>
@@ -22875,7 +22825,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>423</v>
@@ -22887,7 +22837,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>425</v>
@@ -22947,7 +22897,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>436</v>
